--- a/5_Brassica_oleracea_exp/data/novaseq_ernakovich_output/sample_data.xlsx
+++ b/5_Brassica_oleracea_exp/data/novaseq_ernakovich_output/sample_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wageningenur4-my.sharepoint.com/personal/zulema_carracedolorenzo_wur_nl/Documents/Pseudomonas project/Split_pot_experiment/Split_pot_Jul22/Analysis/data/Zulema_novaseq_ernakovich_output/16S/03_tabletax/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.projects\Pseudomonas_VOCs\5_Brassica_oleracea_exp\data\novaseq_ernakovich_output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{9485B21A-32F3-412C-8E1D-EE81A02248D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1F4F299-BAAD-4F91-82D8-E09CFC5A7202}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A811E0FF-9AB7-486C-961D-F62CF8B8FEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{82D8A685-5170-4FF8-9C50-9CF81175F243}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15285" xr2:uid="{82D8A685-5170-4FF8-9C50-9CF81175F243}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -429,9 +429,6 @@
     <t>rhizosphere</t>
   </si>
   <si>
-    <t>bulk_soil</t>
-  </si>
-  <si>
     <t>sample_ID</t>
   </si>
   <si>
@@ -442,6 +439,9 @@
   </si>
   <si>
     <t>failed</t>
+  </si>
+  <si>
+    <t>root_associated</t>
   </si>
 </sst>
 </file>
@@ -811,7 +811,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -850,10 +850,10 @@
         <v>10</v>
       </c>
       <c r="N1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O1" t="s">
         <v>133</v>
-      </c>
-      <c r="O1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -900,7 +900,7 @@
         <v>3.3170000000000002</v>
       </c>
       <c r="O2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -947,7 +947,7 @@
         <v>3.3730000000000002</v>
       </c>
       <c r="O3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -994,7 +994,7 @@
         <v>7.367</v>
       </c>
       <c r="O4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -1085,7 +1085,7 @@
         <v>10.663</v>
       </c>
       <c r="O6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -1176,7 +1176,7 @@
         <v>5.5540000000000003</v>
       </c>
       <c r="O8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -1707,7 +1707,7 @@
         <v>6.3369999999999997</v>
       </c>
       <c r="O20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -1798,7 +1798,7 @@
         <v>2.3069999999999999</v>
       </c>
       <c r="O22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -2065,7 +2065,7 @@
         <v>4.0229999999999997</v>
       </c>
       <c r="O28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -2112,7 +2112,7 @@
         <v>5.0330000000000004</v>
       </c>
       <c r="O29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -2159,7 +2159,7 @@
         <v>2.6030000000000002</v>
       </c>
       <c r="O30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -2250,7 +2250,7 @@
         <v>3.67</v>
       </c>
       <c r="O32" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -2297,7 +2297,7 @@
         <v>8.3119999999999994</v>
       </c>
       <c r="O33" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -2520,7 +2520,7 @@
         <v>1.8440000000000001</v>
       </c>
       <c r="O38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
@@ -2743,7 +2743,7 @@
         <v>2.452</v>
       </c>
       <c r="O43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -2878,7 +2878,7 @@
         <v>8.3059999999999992</v>
       </c>
       <c r="O46" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
@@ -3189,7 +3189,7 @@
         <v>2.3780000000000001</v>
       </c>
       <c r="O53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
@@ -3376,7 +3376,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
@@ -3400,7 +3400,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
@@ -3424,7 +3424,7 @@
         <v>3</v>
       </c>
       <c r="C60" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D60" t="s">
         <v>14</v>
@@ -3448,7 +3448,7 @@
         <v>4</v>
       </c>
       <c r="C61" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
@@ -3472,7 +3472,7 @@
         <v>5</v>
       </c>
       <c r="C62" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D62" t="s">
         <v>14</v>
@@ -3496,7 +3496,7 @@
         <v>6</v>
       </c>
       <c r="C63" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D63" t="s">
         <v>14</v>
@@ -3520,7 +3520,7 @@
         <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D64" t="s">
         <v>14</v>
@@ -3544,7 +3544,7 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D65" t="s">
         <v>14</v>
@@ -3568,7 +3568,7 @@
         <v>9</v>
       </c>
       <c r="C66" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
@@ -3592,7 +3592,7 @@
         <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
@@ -3616,7 +3616,7 @@
         <v>11</v>
       </c>
       <c r="C68" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D68" t="s">
         <v>14</v>
@@ -3640,7 +3640,7 @@
         <v>12</v>
       </c>
       <c r="C69" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D69" t="s">
         <v>14</v>
@@ -3664,7 +3664,7 @@
         <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D70" t="s">
         <v>11</v>
@@ -3688,7 +3688,7 @@
         <v>14</v>
       </c>
       <c r="C71" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
@@ -3712,7 +3712,7 @@
         <v>15</v>
       </c>
       <c r="C72" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D72" t="s">
         <v>14</v>
@@ -3736,7 +3736,7 @@
         <v>16</v>
       </c>
       <c r="C73" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D73" t="s">
         <v>14</v>
@@ -3760,7 +3760,7 @@
         <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D74" t="s">
         <v>14</v>
@@ -3784,7 +3784,7 @@
         <v>18</v>
       </c>
       <c r="C75" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D75" t="s">
         <v>11</v>
@@ -3808,7 +3808,7 @@
         <v>19</v>
       </c>
       <c r="C76" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D76" t="s">
         <v>11</v>
@@ -3832,7 +3832,7 @@
         <v>20</v>
       </c>
       <c r="C77" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D77" t="s">
         <v>14</v>
@@ -3856,7 +3856,7 @@
         <v>21</v>
       </c>
       <c r="C78" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D78" t="s">
         <v>11</v>
@@ -3880,7 +3880,7 @@
         <v>22</v>
       </c>
       <c r="C79" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D79" t="s">
         <v>11</v>
@@ -3904,7 +3904,7 @@
         <v>23</v>
       </c>
       <c r="C80" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D80" t="s">
         <v>14</v>
@@ -3928,7 +3928,7 @@
         <v>24</v>
       </c>
       <c r="C81" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D81" t="s">
         <v>14</v>
@@ -3952,7 +3952,7 @@
         <v>25</v>
       </c>
       <c r="C82" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D82" t="s">
         <v>11</v>
@@ -3976,7 +3976,7 @@
         <v>26</v>
       </c>
       <c r="C83" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D83" t="s">
         <v>11</v>
@@ -4000,7 +4000,7 @@
         <v>27</v>
       </c>
       <c r="C84" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D84" t="s">
         <v>11</v>
@@ -4024,7 +4024,7 @@
         <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D85" t="s">
         <v>11</v>
@@ -4048,7 +4048,7 @@
         <v>29</v>
       </c>
       <c r="C86" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D86" t="s">
         <v>11</v>
@@ -4072,7 +4072,7 @@
         <v>30</v>
       </c>
       <c r="C87" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D87" t="s">
         <v>11</v>
@@ -4096,7 +4096,7 @@
         <v>31</v>
       </c>
       <c r="C88" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D88" t="s">
         <v>11</v>
@@ -4117,7 +4117,7 @@
         <v>32</v>
       </c>
       <c r="C89" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D89" t="s">
         <v>14</v>
@@ -4141,7 +4141,7 @@
         <v>33</v>
       </c>
       <c r="C90" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D90" t="s">
         <v>14</v>
@@ -4165,7 +4165,7 @@
         <v>34</v>
       </c>
       <c r="C91" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D91" t="s">
         <v>14</v>
@@ -4189,7 +4189,7 @@
         <v>35</v>
       </c>
       <c r="C92" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D92" t="s">
         <v>11</v>
@@ -4213,7 +4213,7 @@
         <v>36</v>
       </c>
       <c r="C93" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D93" t="s">
         <v>14</v>
@@ -4237,7 +4237,7 @@
         <v>37</v>
       </c>
       <c r="C94" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D94" t="s">
         <v>11</v>
@@ -4261,7 +4261,7 @@
         <v>38</v>
       </c>
       <c r="C95" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D95" t="s">
         <v>11</v>
@@ -4285,7 +4285,7 @@
         <v>39</v>
       </c>
       <c r="C96" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D96" t="s">
         <v>14</v>
@@ -4309,7 +4309,7 @@
         <v>40</v>
       </c>
       <c r="C97" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D97" t="s">
         <v>11</v>
@@ -4333,7 +4333,7 @@
         <v>41</v>
       </c>
       <c r="C98" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D98" t="s">
         <v>14</v>
@@ -4357,7 +4357,7 @@
         <v>42</v>
       </c>
       <c r="C99" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D99" t="s">
         <v>11</v>
@@ -4381,7 +4381,7 @@
         <v>43</v>
       </c>
       <c r="C100" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D100" t="s">
         <v>14</v>
@@ -4405,7 +4405,7 @@
         <v>44</v>
       </c>
       <c r="C101" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D101" t="s">
         <v>11</v>
@@ -4429,7 +4429,7 @@
         <v>45</v>
       </c>
       <c r="C102" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D102" t="s">
         <v>14</v>
@@ -4453,7 +4453,7 @@
         <v>46</v>
       </c>
       <c r="C103" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D103" t="s">
         <v>14</v>
@@ -4477,7 +4477,7 @@
         <v>47</v>
       </c>
       <c r="C104" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D104" t="s">
         <v>11</v>
@@ -4501,7 +4501,7 @@
         <v>48</v>
       </c>
       <c r="C105" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D105" t="s">
         <v>11</v>
@@ -4525,7 +4525,7 @@
         <v>49</v>
       </c>
       <c r="C106" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D106" t="s">
         <v>14</v>
@@ -4549,7 +4549,7 @@
         <v>50</v>
       </c>
       <c r="C107" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D107" t="s">
         <v>14</v>
@@ -4573,7 +4573,7 @@
         <v>51</v>
       </c>
       <c r="C108" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D108" t="s">
         <v>14</v>
@@ -4597,7 +4597,7 @@
         <v>52</v>
       </c>
       <c r="C109" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D109" t="s">
         <v>11</v>
@@ -4621,7 +4621,7 @@
         <v>53</v>
       </c>
       <c r="C110" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D110" t="s">
         <v>14</v>
@@ -4645,7 +4645,7 @@
         <v>54</v>
       </c>
       <c r="C111" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D111" t="s">
         <v>14</v>
@@ -4669,7 +4669,7 @@
         <v>55</v>
       </c>
       <c r="C112" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D112" t="s">
         <v>14</v>
@@ -4693,7 +4693,7 @@
         <v>56</v>
       </c>
       <c r="C113" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D113" t="s">
         <v>11</v>
